--- a/data/cox_xlsx/CARLb.CO.xlsx
+++ b/data/cox_xlsx/CARLb.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="574">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -1101,13 +1101,19 @@
     <t>Total current liabilities</t>
   </si>
   <si>
-    <t>Bank Borrowings</t>
+    <t>Borrowings LT</t>
+  </si>
+  <si>
+    <t>Bank Borrowings LT</t>
   </si>
   <si>
     <t>Lease Liabilities</t>
   </si>
   <si>
     <t>Other borrowings</t>
+  </si>
+  <si>
+    <t>Mortgages LT</t>
   </si>
   <si>
     <t>Reported Total Long Term Debt</t>
@@ -17178,13 +17184,27 @@
       <c r="A80" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="B80" s="15"/>
-      <c r="C80" s="15"/>
-      <c r="D80" s="15"/>
-      <c r="E80" s="15"/>
-      <c r="F80" s="15"/>
-      <c r="G80" s="15"/>
-      <c r="H80" s="15"/>
+      <c r="B80" s="15">
+        <v>13542.61</v>
+      </c>
+      <c r="C80" s="15">
+        <v>16243.249999999998</v>
+      </c>
+      <c r="D80" s="15">
+        <v>11812.43</v>
+      </c>
+      <c r="E80" s="15">
+        <v>7602.6</v>
+      </c>
+      <c r="F80" s="15">
+        <v>7798.860000000001</v>
+      </c>
+      <c r="G80" s="15">
+        <v>789.87</v>
+      </c>
+      <c r="H80" s="15">
+        <v>4859.610000000001</v>
+      </c>
       <c r="I80" s="15"/>
       <c r="J80" s="15"/>
       <c r="K80" s="15"/>
@@ -17293,27 +17313,13 @@
       <c r="A83" s="14" t="s">
         <v>342</v>
       </c>
-      <c r="B83" s="15">
-        <v>14507.57</v>
-      </c>
-      <c r="C83" s="15">
-        <v>16961.28</v>
-      </c>
-      <c r="D83" s="15">
-        <v>12511.69</v>
-      </c>
-      <c r="E83" s="19">
-        <v>8152.59</v>
-      </c>
-      <c r="F83" s="19">
-        <v>8303.79</v>
-      </c>
-      <c r="G83" s="19">
-        <v>1350.24</v>
-      </c>
-      <c r="H83" s="19">
-        <v>5418.31</v>
-      </c>
+      <c r="B83" s="15"/>
+      <c r="C83" s="15"/>
+      <c r="D83" s="15"/>
+      <c r="E83" s="19"/>
+      <c r="F83" s="19"/>
+      <c r="G83" s="19"/>
+      <c r="H83" s="19"/>
       <c r="I83" s="19">
         <v>9597.08</v>
       </c>
@@ -18232,8 +18238,8 @@
       </c>
     </row>
     <row r="101" ht="15.0" customHeight="1">
-      <c r="A101" s="14" t="s">
-        <v>342</v>
+      <c r="A101" s="23" t="s">
+        <v>360</v>
       </c>
       <c r="B101" s="15">
         <v>97210.65</v>
@@ -18374,8 +18380,8 @@
       </c>
     </row>
     <row r="103" ht="15.0" customHeight="1">
-      <c r="A103" s="14" t="s">
-        <v>360</v>
+      <c r="A103" s="23" t="s">
+        <v>361</v>
       </c>
       <c r="B103" s="19">
         <v>469.82</v>
@@ -18446,7 +18452,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B104" s="19">
         <v>3643.11</v>
@@ -18503,7 +18509,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B105" s="20">
         <v>28.47</v>
@@ -18557,8 +18563,8 @@
       <c r="W105" s="15"/>
     </row>
     <row r="106" ht="15.0" customHeight="1">
-      <c r="A106" s="14" t="s">
-        <v>358</v>
+      <c r="A106" s="23" t="s">
+        <v>364</v>
       </c>
       <c r="B106" s="15"/>
       <c r="C106" s="15"/>
@@ -18613,7 +18619,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B107" s="15"/>
       <c r="C107" s="15"/>
@@ -18713,7 +18719,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B109" s="15">
         <v>13722.94</v>
@@ -18855,7 +18861,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B111" s="20">
         <v>11.07</v>
@@ -18908,7 +18914,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B112" s="19">
         <v>2936.0</v>
@@ -19032,7 +19038,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="17" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B114" s="18">
         <v>118219.81</v>
@@ -19103,7 +19109,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B115" s="15"/>
       <c r="C115" s="15"/>
@@ -19148,7 +19154,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="17" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B116" s="18">
         <v>195014.52</v>
@@ -19219,7 +19225,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B117" s="19">
         <v>4196.77</v>
@@ -19290,7 +19296,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B118" s="21">
         <v>-5052.57</v>
@@ -19345,7 +19351,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B119" s="21">
         <v>-5448.05</v>
@@ -19408,7 +19414,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B120" s="19">
         <v>395.47</v>
@@ -19463,7 +19469,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B121" s="15"/>
       <c r="C121" s="15"/>
@@ -19494,7 +19500,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B122" s="15"/>
       <c r="C122" s="15"/>
@@ -19529,7 +19535,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B123" s="15">
         <v>44838.83</v>
@@ -19600,7 +19606,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B124" s="15"/>
       <c r="C124" s="15"/>
@@ -19635,7 +19641,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="17" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B125" s="18">
         <v>43983.03</v>
@@ -19777,7 +19783,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="17" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B127" s="24">
         <v>4543.2</v>
@@ -19848,7 +19854,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B128" s="18">
         <v>48526.23</v>
@@ -19919,7 +19925,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B129" s="15"/>
       <c r="C129" s="15"/>
@@ -19948,7 +19954,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B130" s="18">
         <v>243540.75</v>
@@ -20019,7 +20025,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B131" s="19">
         <v>132.66</v>
@@ -20090,7 +20096,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B132" s="19">
         <v>132.17</v>
@@ -20161,7 +20167,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B133" s="20">
         <v>0.48</v>
@@ -20232,7 +20238,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B134" s="15"/>
       <c r="C134" s="15"/>
@@ -20265,7 +20271,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B135" s="15"/>
       <c r="C135" s="15"/>
@@ -20304,7 +20310,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B136" s="19">
         <v>3163.79</v>
@@ -20341,7 +20347,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B137" s="15"/>
       <c r="C137" s="15"/>
@@ -20386,7 +20392,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B138" s="19">
         <v>740.33</v>
@@ -20435,7 +20441,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B139" s="19">
         <v>550.5</v>
@@ -20484,7 +20490,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="14" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B140" s="19">
         <v>370.16</v>
@@ -20533,7 +20539,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B141" s="19">
         <v>287.91</v>
@@ -20582,7 +20588,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B142" s="19">
         <v>1694.21</v>
@@ -20631,7 +20637,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B143" s="19">
         <v>4290.1</v>
@@ -20672,7 +20678,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B144" s="15">
         <v>17010.12</v>
@@ -20733,7 +20739,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B145" s="19">
         <v>9059.52</v>
@@ -20792,7 +20798,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B146" s="15">
         <v>17726.72</v>
@@ -20851,7 +20857,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B147" s="19">
         <v>6841.7</v>
@@ -20912,7 +20918,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B148" s="15">
         <v>42929.48</v>
@@ -20973,7 +20979,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B149" s="15"/>
       <c r="C149" s="15"/>
@@ -21024,7 +21030,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B150" s="15">
         <v>20392.22</v>
@@ -21055,7 +21061,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B151" s="20">
         <v>0.48</v>
@@ -21126,7 +21132,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B152" s="20">
         <v>98.47</v>
@@ -21197,7 +21203,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B153" s="20">
         <v>98.96</v>
@@ -21268,7 +21274,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B154" s="20">
         <v>0.75</v>
@@ -21339,7 +21345,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B155" s="20">
         <v>33.7</v>
@@ -21410,7 +21416,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B156" s="20">
         <v>33.7</v>
@@ -21481,7 +21487,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B157" s="20">
         <v>0.25</v>
@@ -21552,7 +21558,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="14" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B158" s="19">
         <v>494.79</v>
@@ -21583,7 +21589,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="14" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B159" s="20">
         <v>2.42</v>
@@ -21614,7 +21620,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B160" s="19">
         <v>492.36</v>
@@ -22504,7 +22510,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -22890,70 +22896,70 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -23029,7 +23035,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -23198,7 +23204,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B21" s="19">
         <v>8512.83</v>
@@ -23269,7 +23275,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -23320,7 +23326,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B23" s="21">
         <v>-897.08</v>
@@ -23434,7 +23440,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B25" s="21">
         <v>-131.74</v>
@@ -23536,7 +23542,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -23567,7 +23573,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B28" s="20">
         <v>15.68</v>
@@ -23610,7 +23616,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B29" s="20">
         <v>53.32</v>
@@ -23641,7 +23647,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -23686,7 +23692,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B31" s="19">
         <v>1144.87</v>
@@ -23800,7 +23806,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B33" s="19">
         <v>1328.37</v>
@@ -23861,7 +23867,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B34" s="21">
         <v>-754.36</v>
@@ -23922,7 +23928,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B35" s="21">
         <v>-2027.84</v>
@@ -23975,7 +23981,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B36" s="21">
         <v>-487.75</v>
@@ -24022,7 +24028,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B37" s="21">
         <v>-748.09</v>
@@ -24069,7 +24075,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B38" s="21">
         <v>-781.02</v>
@@ -24130,7 +24136,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B39" s="22">
         <v>-10.98</v>
@@ -24191,7 +24197,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B40" s="21">
         <v>-2165.85</v>
@@ -24262,7 +24268,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B41" s="19">
         <v>534.8</v>
@@ -24333,7 +24339,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B42" s="21">
         <v>-2622.23</v>
@@ -24404,7 +24410,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B43" s="21">
         <v>-3930.21</v>
@@ -24506,7 +24512,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -24547,7 +24553,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -24588,7 +24594,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="17" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B47" s="18">
         <v>19495.77</v>
@@ -24659,7 +24665,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B48" s="21">
         <v>-7722.4</v>
@@ -24730,7 +24736,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B49" s="19">
         <v>166.24</v>
@@ -24785,7 +24791,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B50" s="19">
         <v>103.51</v>
@@ -24854,7 +24860,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B51" s="15"/>
       <c r="C51" s="19">
@@ -24907,7 +24913,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B52" s="22">
         <v>-23.52</v>
@@ -24962,7 +24968,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B53" s="20">
         <v>37.64</v>
@@ -25013,7 +25019,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B54" s="22">
         <v>-95.67</v>
@@ -25068,7 +25074,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B55" s="19">
         <v>959.81</v>
@@ -25123,7 +25129,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B56" s="16">
         <v>-46141.5</v>
@@ -25152,7 +25158,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -25205,7 +25211,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -25254,7 +25260,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -25291,7 +25297,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
@@ -25328,7 +25334,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -25371,7 +25377,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -25414,7 +25420,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
@@ -25457,7 +25463,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -25494,7 +25500,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -25531,7 +25537,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -25568,7 +25574,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B67" s="19">
         <v>287.0</v>
@@ -25607,7 +25613,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
@@ -25644,7 +25650,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
@@ -25679,7 +25685,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B70" s="15"/>
       <c r="C70" s="15"/>
@@ -25708,7 +25714,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B71" s="21">
         <v>-1047.64</v>
@@ -25739,7 +25745,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B72" s="15">
         <v>0.0</v>
@@ -25770,7 +25776,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="17" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B73" s="25">
         <v>-53476.53</v>
@@ -25902,7 +25908,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B75" s="15"/>
       <c r="C75" s="15"/>
@@ -25945,7 +25951,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B76" s="15"/>
       <c r="C76" s="15"/>
@@ -25984,7 +25990,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B77" s="15"/>
       <c r="C77" s="15"/>
@@ -26088,7 +26094,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -26119,7 +26125,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B80" s="15"/>
       <c r="C80" s="15"/>
@@ -26150,7 +26156,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
@@ -26179,7 +26185,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B82" s="15">
         <v>0.0</v>
@@ -26220,7 +26226,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B83" s="15">
         <v>38811.18</v>
@@ -26281,7 +26287,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
@@ -26322,7 +26328,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B85" s="15"/>
       <c r="C85" s="15"/>
@@ -26355,7 +26361,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B86" s="15"/>
       <c r="C86" s="15"/>
@@ -26384,7 +26390,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B87" s="15"/>
       <c r="C87" s="15"/>
@@ -26415,7 +26421,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B88" s="15"/>
       <c r="C88" s="15"/>
@@ -26456,7 +26462,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B89" s="15"/>
       <c r="C89" s="15"/>
@@ -26485,7 +26491,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B90" s="15"/>
       <c r="C90" s="15"/>
@@ -26559,7 +26565,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
@@ -26590,7 +26596,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B93" s="15"/>
       <c r="C93" s="15"/>
@@ -26621,7 +26627,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B94" s="15"/>
       <c r="C94" s="15"/>
@@ -26656,7 +26662,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B95" s="15"/>
       <c r="C95" s="15"/>
@@ -26693,7 +26699,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B96" s="15"/>
       <c r="C96" s="15"/>
@@ -26730,7 +26736,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B97" s="15"/>
       <c r="C97" s="15"/>
@@ -26761,7 +26767,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B98" s="15"/>
       <c r="C98" s="15"/>
@@ -26792,7 +26798,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B99" s="15"/>
       <c r="C99" s="15"/>
@@ -26829,7 +26835,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B100" s="15"/>
       <c r="C100" s="15"/>
@@ -26860,7 +26866,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B101" s="15"/>
       <c r="C101" s="15"/>
@@ -26889,7 +26895,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B102" s="15"/>
       <c r="C102" s="15"/>
@@ -26918,7 +26924,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B103" s="15"/>
       <c r="C103" s="15"/>
@@ -26947,7 +26953,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="17" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B104" s="18">
         <v>31852.55</v>
@@ -27018,7 +27024,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B105" s="15">
         <v>0.0</v>
@@ -27055,7 +27061,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B106" s="21">
         <v>-944.13</v>
@@ -27126,7 +27132,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B107" s="15">
         <v>18207.62</v>
@@ -27197,7 +27203,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B108" s="15">
         <v>15108.69</v>
@@ -27268,7 +27274,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B109" s="21">
         <v>-2128.21</v>
@@ -27323,7 +27329,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="17" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B110" s="26">
         <v>-3072.34</v>
@@ -27394,7 +27400,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B111" s="15"/>
       <c r="C111" s="15"/>
@@ -27427,7 +27433,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B112" s="15"/>
       <c r="C112" s="15">
@@ -28377,7 +28383,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -28556,37 +28562,37 @@
         <v>39</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AE11" s="7" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AF11" s="7" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG11" s="7" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AH11" s="7" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -29111,7 +29117,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -29218,42 +29224,42 @@
         <v>71</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AE19" s="13" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AF19" s="13" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AG19" s="13" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AH19" s="13" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="28" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B20" s="29"/>
       <c r="C20" s="29"/>
@@ -29291,7 +29297,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="30" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B21" s="31">
         <v>281951.78</v>
@@ -29393,7 +29399,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="30" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B22" s="31">
         <v>256064.14</v>
@@ -29479,7 +29485,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="28" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B23" s="29"/>
       <c r="C23" s="29"/>
@@ -29517,7 +29523,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="30" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B24" s="31">
         <v>180852.83</v>
@@ -29621,7 +29627,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="30" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B25" s="31">
         <v>202917.51</v>
@@ -29717,7 +29723,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="28" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B26" s="29"/>
       <c r="C26" s="29"/>
@@ -29755,7 +29761,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="30" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B27" s="32">
         <v>1321.2</v>
@@ -29859,7 +29865,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="30" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B28" s="32">
         <v>1399.88</v>
@@ -29955,7 +29961,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="28" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B29" s="29"/>
       <c r="C29" s="29"/>
@@ -29993,7 +29999,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="30" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B30" s="33">
         <v>6.73</v>
@@ -30095,7 +30101,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="30" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B31" s="33">
         <v>6.63</v>
@@ -30181,7 +30187,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="28" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
@@ -30219,7 +30225,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="30" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B33" s="33">
         <v>3.23</v>
@@ -30321,7 +30327,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="30" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B34" s="33">
         <v>2.87</v>
@@ -30407,7 +30413,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="30" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B35" s="33">
         <v>3.23</v>
@@ -30511,7 +30517,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="30" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B36" s="33">
         <v>2.87</v>
@@ -30607,7 +30613,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="28" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29"/>
@@ -30645,7 +30651,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="30" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B38" s="35">
         <v>3.97</v>
@@ -30747,7 +30753,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="30" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B39" s="35">
         <v>3.9</v>
@@ -30833,7 +30839,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="28" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="29"/>
@@ -30871,7 +30877,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="30" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B41" s="31"/>
       <c r="C41" s="31"/>
@@ -30927,7 +30933,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="30" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B42" s="31"/>
       <c r="C42" s="31"/>
@@ -30975,7 +30981,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="28" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B43" s="29"/>
       <c r="C43" s="29"/>
@@ -31013,7 +31019,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="30" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B44" s="35">
         <v>1.24</v>
@@ -31117,7 +31123,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="30" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B45" s="35">
         <v>1.64</v>
@@ -31213,7 +31219,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="28" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B46" s="29"/>
       <c r="C46" s="29"/>
@@ -31251,7 +31257,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="30" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B47" s="35">
         <v>14.86</v>
@@ -31343,7 +31349,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="30" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B48" s="35">
         <v>15.08</v>
@@ -31427,7 +31433,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="28" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B49" s="29"/>
       <c r="C49" s="29"/>
@@ -31465,7 +31471,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="30" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B50" s="35">
         <v>8.85</v>
@@ -31569,7 +31575,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="30" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B51" s="35">
         <v>9.8</v>
@@ -31665,7 +31671,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="28" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B52" s="29"/>
       <c r="C52" s="29"/>
@@ -31703,7 +31709,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="30" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B53" s="35">
         <v>18.59</v>
@@ -31805,7 +31811,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="30" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B54" s="35">
         <v>16.87</v>
@@ -31901,7 +31907,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="28" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B55" s="29"/>
       <c r="C55" s="29"/>
@@ -31939,7 +31945,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="30" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B56" s="35">
         <v>13.53</v>
@@ -32043,7 +32049,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="30" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B57" s="35">
         <v>3.9</v>
@@ -32129,7 +32135,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="28" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B58" s="29"/>
       <c r="C58" s="29"/>
@@ -32167,7 +32173,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="30" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B59" s="36">
         <v>-0.54</v>
@@ -32267,7 +32273,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="30" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B60" s="35">
         <v>9.36</v>
@@ -32357,7 +32363,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="28" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B61" s="29"/>
       <c r="C61" s="29"/>
@@ -32395,7 +32401,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="30" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B62" s="35">
         <v>2.0</v>
@@ -32497,7 +32503,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="30" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B63" s="35">
         <v>2.2</v>
@@ -32583,7 +32589,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="28" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B64" s="29"/>
       <c r="C64" s="29"/>
@@ -32621,7 +32627,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="30" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B65" s="35">
         <v>9.65</v>
@@ -32715,7 +32721,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="30" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B66" s="35">
         <v>10.34</v>
@@ -32791,7 +32797,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="28" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B67" s="29"/>
       <c r="C67" s="29"/>
@@ -32829,7 +32835,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="30" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B68" s="35">
         <v>13.67</v>
@@ -32931,7 +32937,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="30" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B69" s="35">
         <v>12.83</v>
@@ -33017,7 +33023,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="28" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B70" s="29"/>
       <c r="C70" s="29"/>
@@ -33055,7 +33061,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="30" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B71" s="35">
         <v>23.92</v>
@@ -33147,7 +33153,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="30" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B72" s="35">
         <v>20.09</v>
